--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-31T15:36:14.650Z</t>
+    <t>2026-03-31T16:37:09.491Z</t>
   </si>
   <si>
     <t>Unify HR, Finance, &amp; IT | HR &amp; Payroll Simplified | Paylocity</t>
